--- a/files/Capex_Model_Base.xlsx
+++ b/files/Capex_Model_Base.xlsx
@@ -7,9 +7,17 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Capex Pipeline" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Capex Summary" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Financials" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Returns" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Assumptions" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Capex Summary'!$A$1:$H$9</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Financials'!$A$1:$L$8</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Returns'!$A$1:$D$8</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Assumptions'!$A$1:$D$10</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -17,7 +25,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -26,23 +34,13 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <name val="Aptos"/>
-      <b val="1"/>
-      <color rgb="001F4E78"/>
-      <sz val="14"/>
-    </font>
-    <font>
-      <name val="Aptos"/>
+      <name val="Calibri"/>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
       <sz val="11"/>
     </font>
-    <font>
-      <name val="Aptos"/>
-      <sz val="10"/>
-    </font>
   </fonts>
-  <fills count="4">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
@@ -51,12 +49,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="001F4E78"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00F2F2F2"/>
+        <fgColor rgb="000F4C81"/>
       </patternFill>
     </fill>
   </fills>
@@ -70,30 +63,30 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="00D0D7DE"/>
+        <color rgb="00D1D5DB"/>
       </left>
       <right style="thin">
-        <color rgb="00D0D7DE"/>
+        <color rgb="00D1D5DB"/>
       </right>
       <top style="thin">
-        <color rgb="00D0D7DE"/>
+        <color rgb="00D1D5DB"/>
       </top>
       <bottom style="thin">
-        <color rgb="00D0D7DE"/>
+        <color rgb="00D1D5DB"/>
       </bottom>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -459,399 +452,1362 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G12"/>
+  <dimension ref="A1:H9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="19" customWidth="1" min="1" max="1"/>
-    <col width="19" customWidth="1" min="2" max="2"/>
-    <col width="19" customWidth="1" min="3" max="3"/>
-    <col width="19" customWidth="1" min="4" max="4"/>
-    <col width="19" customWidth="1" min="5" max="5"/>
-    <col width="19" customWidth="1" min="6" max="6"/>
-    <col width="19" customWidth="1" min="7" max="7"/>
+    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Group Capex Model - Base Case FY2026-2028</t>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Year 0</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Year 1</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Year 2</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Year 3</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Total MYR M</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Land &amp; site works</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>42.0</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>42.0</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Project</t>
+          <t>Buildings &amp; civil</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Total cost</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>NPV</t>
+          <t>118.0</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
+          <t>42.0</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>160.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Plant &amp; equipment</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>62.0</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>148.0</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>22.0</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>232.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>IT &amp; automation</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>18.0</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>22.0</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>12.0</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>52.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>Commissioning &amp; ramp</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>24.0</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>18.0</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>42.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>Working capital</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>12.0</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>22.0</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>18.0</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>52.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>Sustaining capex</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>8.0</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>14.0</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>18.0</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>40.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>TOTAL CAPEX</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>42.0</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>210.0</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>258.0</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>78.0</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>14.0</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>18.0</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>620.0</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:H9"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:L8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="8" customWidth="1" min="3" max="3"/>
+    <col width="8" customWidth="1" min="4" max="4"/>
+    <col width="8" customWidth="1" min="5" max="5"/>
+    <col width="8" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="8" customWidth="1" min="8" max="8"/>
+    <col width="8" customWidth="1" min="9" max="9"/>
+    <col width="8" customWidth="1" min="10" max="10"/>
+    <col width="8" customWidth="1" min="11" max="11"/>
+    <col width="8" customWidth="1" min="12" max="12"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>MYR M</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Y0</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Y1</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Y2</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Y3</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Y4</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Y5</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Y6</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Y7</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Y8</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Y9</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Y10</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Revenue</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>82</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>248</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>384</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>468</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>504</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>522</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>540</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>558</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>578</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>EBITDA</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>108</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>138</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>152</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>158</t>
+        </is>
+      </c>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>164</t>
+        </is>
+      </c>
+      <c r="K3" s="2" t="inlineStr">
+        <is>
+          <t>170</t>
+        </is>
+      </c>
+      <c r="L3" s="2" t="inlineStr">
+        <is>
+          <t>178</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>EBITDA margin</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>15%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>23%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>28%</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>29%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>30%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>30%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>30%</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>30%</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>31%</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>Capex</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>(42)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>(210)</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>(258)</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>(78)</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>(14)</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>(18)</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>(8)</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>(8)</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>(8)</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>(8)</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>(8)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>Tax</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>(2)</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>(10)</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>(20)</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>(26)</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>(28)</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>(30)</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>(31)</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>(32)</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>(34)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>Working capital movement</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>(12)</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>(22)</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>(18)</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>(6)</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>(4)</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>(2)</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>(2)</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>(2)</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>(2)</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>(2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>Free cash flow</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>(42)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>(222)</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>(270)</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>(48)</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>+68</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>+90</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>+114</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>+118</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>+123</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>+128</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>+134</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:L8"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Base Case</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Hurdle</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>NPV @ WACC 8.4% (MYR M)</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>+184</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>&gt;0</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
           <t>IRR</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>Payback</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>Gate status</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="inlineStr">
-        <is>
-          <t>Sponsor</t>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>12.8%</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>&gt;10%</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>Bandar Zava Phase 2</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>MYR 390M</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>MYR +75M</t>
-        </is>
-      </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>17.5%</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>10.4 yrs</t>
-        </is>
-      </c>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t>Awaiting board</t>
-        </is>
-      </c>
-      <c r="G4" s="3" t="inlineStr">
-        <is>
-          <t>Nurul Huda</t>
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Payback (years)</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>5.4</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>&lt;7</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
-        <is>
-          <t>Iskandar Logistics Hub</t>
-        </is>
-      </c>
-      <c r="B5" s="4" t="inlineStr">
-        <is>
-          <t>MYR 535M</t>
-        </is>
-      </c>
-      <c r="C5" s="4" t="inlineStr">
-        <is>
-          <t>MYR +9M</t>
-        </is>
-      </c>
-      <c r="D5" s="4" t="inlineStr">
-        <is>
-          <t>10.4%</t>
-        </is>
-      </c>
-      <c r="E5" s="4" t="inlineStr">
-        <is>
-          <t>7.8 yrs</t>
-        </is>
-      </c>
-      <c r="F5" s="4" t="inlineStr">
-        <is>
-          <t>In FID</t>
-        </is>
-      </c>
-      <c r="G5" s="4" t="inlineStr">
-        <is>
-          <t>Siti Aishah</t>
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>ROIC year 5</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>14.2%</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>&gt;12%</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="inlineStr">
-        <is>
-          <t>Penang Data Centre</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>MYR 829M</t>
-        </is>
-      </c>
-      <c r="C6" s="3" t="inlineStr">
-        <is>
-          <t>MYR +53M</t>
-        </is>
-      </c>
-      <c r="D6" s="3" t="inlineStr">
-        <is>
-          <t>9.8%</t>
-        </is>
-      </c>
-      <c r="E6" s="3" t="inlineStr">
-        <is>
-          <t>9.1 yrs</t>
-        </is>
-      </c>
-      <c r="F6" s="3" t="inlineStr">
-        <is>
-          <t>Awaiting board</t>
-        </is>
-      </c>
-      <c r="G6" s="3" t="inlineStr">
-        <is>
-          <t>Sasha Ouellet</t>
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>ROIC year 10</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>18.6%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>&gt;15%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="inlineStr">
-        <is>
-          <t>KK Hospital Wing C</t>
-        </is>
-      </c>
-      <c r="B7" s="4" t="inlineStr">
-        <is>
-          <t>MYR 397M</t>
-        </is>
-      </c>
-      <c r="C7" s="4" t="inlineStr">
-        <is>
-          <t>MYR +79M</t>
-        </is>
-      </c>
-      <c r="D7" s="4" t="inlineStr">
-        <is>
-          <t>21.7%</t>
-        </is>
-      </c>
-      <c r="E7" s="4" t="inlineStr">
-        <is>
-          <t>9.2 yrs</t>
-        </is>
-      </c>
-      <c r="F7" s="4" t="inlineStr">
-        <is>
-          <t>Awaiting board</t>
-        </is>
-      </c>
-      <c r="G7" s="4" t="inlineStr">
-        <is>
-          <t>Tan Wei Ming</t>
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>NPV/Capex multiple</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>0.30x</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>&gt;0.20</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="inlineStr">
-        <is>
-          <t>Kuching Solar Farm 90MW</t>
-        </is>
-      </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>MYR 627M</t>
-        </is>
-      </c>
-      <c r="C8" s="3" t="inlineStr">
-        <is>
-          <t>MYR +162M</t>
-        </is>
-      </c>
-      <c r="D8" s="3" t="inlineStr">
-        <is>
-          <t>12.6%</t>
-        </is>
-      </c>
-      <c r="E8" s="3" t="inlineStr">
-        <is>
-          <t>11.3 yrs</t>
-        </is>
-      </c>
-      <c r="F8" s="3" t="inlineStr">
-        <is>
-          <t>Awaiting board</t>
-        </is>
-      </c>
-      <c r="G8" s="3" t="inlineStr">
-        <is>
-          <t>Farah Idris</t>
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>Break-even revenue (year 5)</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>MYR 320M</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>Comfortably above</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:D8"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="36" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Assumption</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Base Value</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Sensitivity Tested ±%</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Plant capacity utilisation Y5</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>82%</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>±15%</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>Engineering study</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Selling price growth</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>2.5% p.a.</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>±200bps</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>Strategy team</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Variable cost inflation</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>3.0% p.a.</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>±200bps</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>Operations</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>Energy cost / unit</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>MYR 0.46</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>±25%</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>Energy market</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>Maintenance capex Y3-10</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>4% of revenue</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>Industry benchmark</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>Working capital</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>15% of revenue</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>Current portfolio</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>Tax rate</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>24%</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>Statutory</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="4" t="inlineStr">
-        <is>
-          <t>Klang Port Terminal 3</t>
-        </is>
-      </c>
-      <c r="B9" s="4" t="inlineStr">
-        <is>
-          <t>MYR 863M</t>
-        </is>
-      </c>
-      <c r="C9" s="4" t="inlineStr">
-        <is>
-          <t>MYR -6M</t>
-        </is>
-      </c>
-      <c r="D9" s="4" t="inlineStr">
-        <is>
-          <t>7.1%</t>
-        </is>
-      </c>
-      <c r="E9" s="4" t="inlineStr">
-        <is>
-          <t>11.1 yrs</t>
-        </is>
-      </c>
-      <c r="F9" s="4" t="inlineStr">
-        <is>
-          <t>Approved</t>
-        </is>
-      </c>
-      <c r="G9" s="4" t="inlineStr">
-        <is>
-          <t>Daichi Maruyama</t>
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>WACC</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>8.4%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>±100bps</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>Group Treasury</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="inlineStr">
-        <is>
-          <t>Cyberjaya Tower D</t>
-        </is>
-      </c>
-      <c r="B10" s="3" t="inlineStr">
-        <is>
-          <t>MYR 492M</t>
-        </is>
-      </c>
-      <c r="C10" s="3" t="inlineStr">
-        <is>
-          <t>MYR +122M</t>
-        </is>
-      </c>
-      <c r="D10" s="3" t="inlineStr">
-        <is>
-          <t>18.7%</t>
-        </is>
-      </c>
-      <c r="E10" s="3" t="inlineStr">
-        <is>
-          <t>5.0 yrs</t>
-        </is>
-      </c>
-      <c r="F10" s="3" t="inlineStr">
-        <is>
-          <t>Awaiting board</t>
-        </is>
-      </c>
-      <c r="G10" s="3" t="inlineStr">
-        <is>
-          <t>Mod Admin</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="4" t="inlineStr">
-        <is>
-          <t>Shah Alam Warehouse</t>
-        </is>
-      </c>
-      <c r="B11" s="4" t="inlineStr">
-        <is>
-          <t>MYR 752M</t>
-        </is>
-      </c>
-      <c r="C11" s="4" t="inlineStr">
-        <is>
-          <t>MYR +42M</t>
-        </is>
-      </c>
-      <c r="D11" s="4" t="inlineStr">
-        <is>
-          <t>8.2%</t>
-        </is>
-      </c>
-      <c r="E11" s="4" t="inlineStr">
-        <is>
-          <t>9.3 yrs</t>
-        </is>
-      </c>
-      <c r="F11" s="4" t="inlineStr">
-        <is>
-          <t>In FID</t>
-        </is>
-      </c>
-      <c r="G11" s="4" t="inlineStr">
-        <is>
-          <t>Kumar Subramaniam</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="3" t="inlineStr">
-        <is>
-          <t>JB Petrochem Upgrade</t>
-        </is>
-      </c>
-      <c r="B12" s="3" t="inlineStr">
-        <is>
-          <t>MYR 91M</t>
-        </is>
-      </c>
-      <c r="C12" s="3" t="inlineStr">
-        <is>
-          <t>MYR +23M</t>
-        </is>
-      </c>
-      <c r="D12" s="3" t="inlineStr">
-        <is>
-          <t>15.1%</t>
-        </is>
-      </c>
-      <c r="E12" s="3" t="inlineStr">
-        <is>
-          <t>8.5 yrs</t>
-        </is>
-      </c>
-      <c r="F12" s="3" t="inlineStr">
-        <is>
-          <t>Approved</t>
-        </is>
-      </c>
-      <c r="G12" s="3" t="inlineStr">
-        <is>
-          <t>Tan Wei Ming</t>
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>Terminal value growth</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>2.0%</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>Conservative</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:G1"/>
-  </mergeCells>
+  <autoFilter ref="A1:D10"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>